--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.1543289325507</v>
+        <v>8.962578451539489</v>
       </c>
       <c r="D2" t="n">
-        <v>55.1543289325507</v>
+        <v>8.962578451539489</v>
       </c>
       <c r="E2" t="n">
-        <v>13.68555032931558</v>
+        <v>2.223901928513782</v>
       </c>
       <c r="F2" t="n">
-        <v>15.86485556761916</v>
+        <v>2.578039029738114</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.53184338880661</v>
+        <v>4.311424550681075</v>
       </c>
       <c r="D3" t="n">
-        <v>18.15501512915987</v>
+        <v>2.95018995848848</v>
       </c>
       <c r="E3" t="n">
-        <v>13.68555032931558</v>
+        <v>2.223901928513782</v>
       </c>
       <c r="F3" t="n">
-        <v>15.86485556761916</v>
+        <v>2.578039029738114</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.73053223532725</v>
+        <v>4.181211488240678</v>
       </c>
       <c r="D4" t="n">
-        <v>26.36343919046949</v>
+        <v>4.284058868451293</v>
       </c>
       <c r="E4" t="n">
-        <v>13.68555032931558</v>
+        <v>2.223901928513782</v>
       </c>
       <c r="F4" t="n">
-        <v>15.86485556761916</v>
+        <v>2.578039029738114</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
